--- a/results/log_pv_inst_fit/log_pv_inst_fit_baseline_estimates.xlsx
+++ b/results/log_pv_inst_fit/log_pv_inst_fit_baseline_estimates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,41 +462,11 @@
           <t>baseline-ML_ErrorFE-queen-Running ML_ErrorFE:queen for log_pv_inst_fit ~ (baseline): ['log_income', 'log_hholds', 'log_sunny_hours']</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>baseline-PooledOLS-inverse_distance-Running PooledOLS:inverse_distance for log_pv_inst_fit ~ (baseline): ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>baseline-PooledOLS-k_nearest-Running PooledOLS:k_nearest for log_pv_inst_fit ~ (baseline): ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>baseline-PooledOLS-queen-Running PooledOLS:queen for log_pv_inst_fit ~ (baseline): ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>baseline-PanelRE-inverse_distance-Running PanelRE:inverse_distance for log_pv_inst_fit ~ (baseline): ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>baseline-PanelRE-k_nearest-Running PanelRE:k_nearest for log_pv_inst_fit ~ (baseline): ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>baseline-PanelRE-queen-Running PanelRE:queen for log_pv_inst_fit ~ (baseline): ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>log_income</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,43 +512,13 @@
       <c r="J2" t="inlineStr">
         <is>
           <t>0.238***</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>-1.256***</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-1.256***</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>-1.256***</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>1.960***</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>1.960***</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>1.960***</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>log_hholds</t>
+          <t>Households</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -624,43 +564,13 @@
       <c r="J3" t="inlineStr">
         <is>
           <t>0.003*</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.006</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0.006</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0.006</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>log_sunny_hours</t>
+          <t>Sunny hours</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -706,126 +616,96 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>0.183***</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.437**</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0.437**</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0.437**</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>-0.170***</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>-0.170***</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>-0.170***</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>W_log_income</t>
+          <t>Spatial term, ρ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.533***</t>
+          <t>0.884***</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.718***</t>
+          <t>0.706***</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.927***</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+          <t>0.596***</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.961***</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.784***</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.691***</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W_log_hholds</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>-0.064***</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>-0.009*</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>-0.009***</t>
-        </is>
-      </c>
+          <t>Spatial term, λ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.973***</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.891***</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.840***</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W_log_sunny_hours</t>
+          <t>W(Income)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-0.279***</t>
+          <t>0.533***</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.326***</t>
+          <t>0.718***</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-0.317***</t>
+          <t>0.927***</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -834,858 +714,320 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W_log_pv_inst_fit</t>
+          <t>W(Households)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.884***</t>
+          <t>-0.064***</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.706***</t>
+          <t>-0.009*</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.596***</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0.961***</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0.784***</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0.691***</t>
-        </is>
-      </c>
+          <t>-0.009***</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>r2</t>
+          <t>W(Sunny hours)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.850</t>
+          <t>-0.279***</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.827</t>
+          <t>-0.326***</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.811</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0.848</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0.823</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0.804</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.009</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.288</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>0.391</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0.113</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>0.113</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>0.113</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0.111</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0.111</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0.111</t>
-        </is>
-      </c>
+          <t>-0.317***</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>aic</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-9796.619</t>
+          <t>0.850</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-9378.206</t>
+          <t>0.827</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-9168.218</t>
+          <t>0.811</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-9765.349</t>
+          <t>0.848</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-9279.755</t>
+          <t>0.823</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-9012.171</t>
+          <t>0.804</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-9778.791</t>
+          <t>0.009</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-9187.876</t>
+          <t>0.288</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-8816.659</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>1484.002</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>1484.002</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>1484.002</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2774.612</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2774.612</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2774.612</t>
+          <t>0.391</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>schwarz</t>
+          <t>AIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-9757.151</t>
+          <t>-9796.619</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-9338.738</t>
+          <t>-9378.206</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-9128.751</t>
+          <t>-9168.218</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-9742.796</t>
+          <t>-9765.349</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-9257.202</t>
+          <t>-9279.755</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-8989.618</t>
+          <t>-9012.171</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-9761.876</t>
+          <t>-9778.791</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-9170.962</t>
+          <t>-9187.876</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-8799.745</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>1506.555</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>1506.555</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>1506.555</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2797.165</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2797.165</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2797.165</t>
+          <t>-8816.659</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>llr</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4905.309</t>
+          <t>-9757.151</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4696.103</t>
+          <t>-9338.738</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4591.109</t>
+          <t>-9128.751</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4886.674</t>
+          <t>-9742.796</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>4643.877</t>
+          <t>-9257.202</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4510.086</t>
+          <t>-8989.618</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4892.396</t>
+          <t>-9761.876</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4596.938</t>
+          <t>-9170.962</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4411.330</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>-738.001</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-738.001</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>-738.001</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>-1383.306</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>-1383.306</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>-1383.306</t>
+          <t>-8799.745</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>n_obs</t>
+          <t>Log-Likelihood</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4905.309</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4696.103</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4591.109</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4886.674</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4643.877</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4510.086</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4892.396</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4596.938</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2076</t>
+          <t>4411.330</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>tests</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df  p-value
-0       LM Marginal RE (LM1)    67.279164   1      0.0
-1  LM Marginal Spatial (LM2)    18.259617   1      0.0
-2             LM Joint (LMJ)  4859.899449   2      0.0</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df       p-value
-0       LM Marginal RE (LM1)    67.279164   1  0.000000e+00
-1  LM Marginal Spatial (LM2)     8.095205   1  3.330669e-16
-2             LM Joint (LMJ)  4592.018203   2  0.000000e+00</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df       p-value
-0       LM Marginal RE (LM1)    67.279164   1  0.000000e+00
-1  LM Marginal Spatial (LM2)     7.959140   1  8.881784e-16
-2             LM Joint (LMJ)  4589.833764   2  0.000000e+00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test   Statistic df p-value
-0      LM Conditional Spatial  155.024562  1     0.0
-1  Hausman Specification Test  -140.77575  3     1.0</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test  Statistic df p-value
-0      LM Conditional Spatial  38.701486  1     0.0
-1  Hausman Specification Test -140.77575  3     1.0</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test  Statistic df p-value
-0      LM Conditional Spatial  25.974249  1     0.0
-1  Hausman Specification Test -140.77575  3     1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>outputs</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0         log_income    -0.060781  0.073502  -0.826937  0.408273
-1         log_hholds     0.000728  0.001192   0.610805  0.541329
-2    log_sunny_hours     0.161209  0.034504   4.672229  0.000003
-3       W_log_income     0.532689  0.135095   3.943066   0.00008
-4       W_log_hholds    -0.064207  0.017108  -3.753095  0.000175
-5  W_log_sunny_hours    -0.279305  0.054232  -5.150208       0.0
-6  W_log_pv_inst_fit     0.883682  0.027945  31.622009       0.0</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err   zt_stat      prob
-0         log_income      0.00761  0.075225  0.101158  0.919425
-1         log_hholds     0.000878  0.001278  0.687066  0.492041
-2    log_sunny_hours     0.145962  0.035065  4.162607  0.000031
-3       W_log_income     0.718419  0.092206   7.79144       0.0
-4       W_log_hholds     -0.00922  0.003778 -2.440473  0.014668
-5  W_log_sunny_hours    -0.326191   0.04613 -7.071187       0.0
-6  W_log_pv_inst_fit     0.706195  0.020917  33.76135       0.0</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0         log_income     0.033631  0.075278   0.446754  0.655052
-1         log_hholds     0.001092  0.001336   0.816864  0.414006
-2    log_sunny_hours     0.109131  0.035836   3.045331  0.002324
-3       W_log_income     0.926901  0.086254   10.74619       0.0
-4       W_log_hholds    -0.008542  0.002188  -3.904442  0.000094
-5  W_log_sunny_hours     -0.31744    0.0446  -7.117511       0.0
-6  W_log_pv_inst_fit     0.595593  0.021397  27.835149       0.0</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0         log_income     0.035885  0.025935    1.38366  0.166463
-1         log_hholds     0.000997  0.001196   0.833948   0.40431
-2    log_sunny_hours     0.067249  0.025295   2.658573  0.007847
-3  W_log_pv_inst_fit     0.961428  0.009941  96.717009       0.0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0         log_income     0.413848  0.037331  11.085999       0.0
-1         log_hholds     0.001583  0.001292   1.224891  0.220616
-2    log_sunny_hours     0.021647  0.025366   0.853398  0.393439
-3  W_log_pv_inst_fit       0.7842  0.015862  49.437376       0.0</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0         log_income     0.610017  0.041156  14.822211       0.0
-1         log_hholds     0.001686  0.001363   1.236602  0.216235
-2    log_sunny_hours     0.001051  0.026693   0.039356  0.968607
-3  W_log_pv_inst_fit     0.690895  0.017247  40.057835       0.0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err     zt_stat      prob
-0       log_income    -0.043036  0.073276   -0.587308  0.556997
-1       log_hholds     0.001147  0.001189    0.964552  0.334769
-2  log_sunny_hours      0.16145  0.034549    4.673092  0.000003
-3           lambda     0.972878  0.007567  128.564364       0.0</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0       log_income      0.15508  0.072079   2.151527  0.031435
-1       log_hholds     0.002167  0.001221   1.775268  0.075854
-2  log_sunny_hours     0.185508  0.035295   5.255858       0.0
-3           lambda     0.891036  0.010036  88.787689       0.0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err   zt_stat      prob
-0       log_income     0.237598  0.071934  3.302979  0.000957
-1       log_hholds     0.002816  0.001206  2.335558  0.019514
-2  log_sunny_hours     0.183218   0.03655  5.012805  0.000001
-3           lambda      0.84007  0.012343  68.06153       0.0</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     7.102933   0.52621  13.498279       0.0
-1       log_income    -1.255648  0.078369 -16.022215       0.0
-2       log_hholds     0.005928  0.009168   0.646563  0.517986
-3  log_sunny_hours     0.436766  0.165426   2.640256  0.008347</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     7.102933   0.52621  13.498279       0.0
-1       log_income    -1.255648  0.078369 -16.022215       0.0
-2       log_hholds     0.005928  0.009168   0.646563  0.517986
-3  log_sunny_hours     0.436766  0.165426   2.640256  0.008347</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     7.102933   0.52621  13.498279       0.0
-1       log_income    -1.255648  0.078369 -16.022215       0.0
-2       log_hholds     0.005928  0.009168   0.646563  0.517986
-3  log_sunny_hours     0.436766  0.165426   2.640256  0.008347</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT    -4.711063  0.203129 -23.192502       0.0
-1       log_income     1.960387  0.042448   46.18296       0.0
-2       log_hholds     0.000192  0.002213   0.086867  0.930777
-3  log_sunny_hours    -0.169947  0.043272    -3.9274  0.000086</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT    -4.711063  0.203129 -23.192502       0.0
-1       log_income     1.960387  0.042448   46.18296       0.0
-2       log_hholds     0.000192  0.002213   0.086867  0.930777
-3  log_sunny_hours    -0.169947  0.043272    -3.9274  0.000086</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT    -4.711063  0.203129 -23.192502       0.0
-1       log_income     1.960387  0.042448   46.18296       0.0
-2       log_hholds     0.000192  0.002213   0.086867  0.930777
-3  log_sunny_hours    -0.169947  0.043272    -3.9274  0.000086</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>effects</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_inverse_distance  \
-log_income                                   4.057060   
-log_hholds                                  -0.545734   
-log_sunny_hours                             -1.015286   
-                 direct_ML_LagFE(SLX)_inverse_distance  \
-log_income                                   -0.060781   
-log_hholds                                    0.000728   
-log_sunny_hours                               0.161209   
-                 indirect_ML_LagFE(SLX)_inverse_distance  
-log_income                                      4.117841  
-log_hholds                                     -0.546462  
-log_sunny_hours                                -1.176495  </t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_k_nearest  \
-log_income                            2.471124   
-log_hholds                           -0.028392   
-log_sunny_hours                      -0.613430   
-                 direct_ML_LagFE(SLX)_k_nearest  \
-log_income                             0.007610   
-log_hholds                             0.000878   
-log_sunny_hours                        0.145962   
-                 indirect_ML_LagFE(SLX)_k_nearest  
-log_income                               2.463514  
-log_hholds                              -0.029270  
-log_sunny_hours                         -0.759392  </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_queen  direct_ML_LagFE(SLX)_queen  \
-log_income                        2.375158                    0.033631   
-log_hholds                       -0.018424                    0.001092   
-log_sunny_hours                  -0.515098                    0.109131   
-                 indirect_ML_LagFE(SLX)_queen  
-log_income                           2.341527  
-log_hholds                          -0.019516  
-log_sunny_hours                     -0.624229  </t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_inverse_distance  \
-log_income                              0.930347   
-log_hholds                              0.025856   
-log_sunny_hours                         1.743490   
-                 direct_ML_LagFE_inverse_distance  \
-log_income                               0.035885   
-log_hholds                               0.000997   
-log_sunny_hours                          0.067249   
-                 indirect_ML_LagFE_inverse_distance  
-log_income                                 0.894462  
-log_hholds                                 0.024859  
-log_sunny_hours                            1.676241  </t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_k_nearest  direct_ML_LagFE_k_nearest  \
-log_income                       1.917741                   0.413848   
-log_hholds                       0.007335                   0.001583   
-log_sunny_hours                  0.100311                   0.021647   
-                 indirect_ML_LagFE_k_nearest  
-log_income                          1.503892  
-log_hholds                          0.005752  
-log_sunny_hours                     0.078664  </t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_queen  direct_ML_LagFE_queen  \
-log_income                   1.973496               0.610017   
-log_hholds                   0.005453               0.001686   
-log_sunny_hours              0.003399               0.001051   
-                 indirect_ML_LagFE_queen  
-log_income                      1.363479  
-log_hholds                      0.003768  
-log_sunny_hours                 0.002348  </t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>lambda</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>0.973***</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>0.891***</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>0.840***</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>CONSTANT</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>7.103***</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>7.103***</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>7.103***</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>-4.711***</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>-4.711***</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>-4.711***</t>
+          <t>N obs.</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2076</t>
         </is>
       </c>
     </row>
